--- a/publishing/accessibility/springer_alt_text_inventory.xlsx
+++ b/publishing/accessibility/springer_alt_text_inventory.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb04d350eb2c34cac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R0e158dcf390642db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R78512e494ce34d44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0f290d3c2043460e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt Text" sheetId="2" r:id="R0e6d76ccec04478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guidance" sheetId="3" r:id="R0adf59027e374c1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,7 +323,7 @@
         <x:v>Generated at UTC</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>46191.10914256945</x:v>
+        <x:v>46192.32035923611</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9235,7 +9235,7 @@
         <x:v>41-4</x:v>
       </x:c>
       <x:c r="I133" s="4" t="str">
-        <x:v>Figure 41-4. Example of a multi-chart infographic sample from the dataset (Shark Attacks)</x:v>
+        <x:v>Figure 41-4. Example of a multi-chart infographic sample from the dataset (Shark Attacks), consisting of four distinct subcharts covering three categories of statistics: historical shark-attack county ranking in the United States, state-level shark attacks in the last ten years, and average annual accidental deaths in the United States</x:v>
       </x:c>
       <x:c r="J133" s="4" t="str">
         <x:v>Figure 41-4: Shark-attack compound infographic example</x:v>
@@ -9253,7 +9253,7 @@
         <x:v>jpg</x:v>
       </x:c>
       <x:c r="O133" s="4" t="str">
-        <x:v>. Example of a multi-chart infographic sample from the dataset (Shark Attacks).</x:v>
+        <x:v>. Example of a multi-chart infographic sample from the dataset (Shark Attacks), consisting of four distinct subcharts covering three categories of statistics: historical shark-attack county ranking in the United States, state-level shark attacks in the last ten years, and average annual accidental deaths in the United States.</x:v>
       </x:c>
       <x:c r="P133" s="4" t="str"/>
       <x:c r="Q133" s="4" t="str">
@@ -9265,7 +9265,7 @@
       <x:c r="S133" s="4" t="str"/>
       <x:c r="T133" s="4" t="str"/>
       <x:c r="U133" s="4" t="str">
-        <x:v>Figure 41-4：多图表信息图样本（鲨鱼袭击）</x:v>
+        <x:v>Figure 41-4：多图表信息图样本（鲨鱼袭击）。该信息图包含四个独立子图，内容涉及美国历史累计鲨鱼袭击县域排行榜、美国近 10 年各州鲨鱼袭击汇总统计、全美年均意外死亡人数统计</x:v>
       </x:c>
       <x:c r="V133" s="4" t="str">
         <x:v>图41-4：多图表信息图样本（鲨鱼袭击）</x:v>
@@ -9297,7 +9297,7 @@
         <x:v>41-5</x:v>
       </x:c>
       <x:c r="I134" s="4" t="str">
-        <x:v>Figure 41-5. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset</x:v>
+        <x:v>Figure 41-5. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset: collecting and filtering real compound infographics, manually partitioning subchart regions, designing layered question chains, and cross-checking answers</x:v>
       </x:c>
       <x:c r="J134" s="4" t="str">
         <x:v>Figure 41-5: Multi-chart infographic dataset construction pipeline</x:v>
@@ -9315,7 +9315,7 @@
         <x:v>png</x:v>
       </x:c>
       <x:c r="O134" s="4" t="str">
-        <x:v>. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset.</x:v>
+        <x:v>. Overview of the four-stage data construction pipeline for the Multi-Chart Infographic Reasoning Dataset: collecting and filtering real compound infographics, manually partitioning subchart regions, designing layered question chains, and cross-checking answers.</x:v>
       </x:c>
       <x:c r="P134" s="4" t="str">
         <x:v>Review against the figure and surrounding text in Chapter 41: Visual Reasoning Data Engineering: Chart Evidence, Medical Images, and Tool-Call Trajectories; expand if Springer requests a longer description for the visual relationships, axes, or sequence.</x:v>
@@ -9329,7 +9329,7 @@
       <x:c r="S134" s="4" t="str"/>
       <x:c r="T134" s="4" t="str"/>
       <x:c r="U134" s="4" t="str">
-        <x:v>Figure 41-5：多图标信息图推理数据集四阶段构建流水线图</x:v>
+        <x:v>Figure 41-5：多图标信息图推理数据集四阶段构建流水线图。该流水线包括原始信息图爬取筛选、多子图区域人工划分、链式问题分层设计、答案人工核验标注四大工序</x:v>
       </x:c>
       <x:c r="V134" s="4" t="str">
         <x:v>图41-5：多图标信息图推理数据集四阶段构建流水线图</x:v>
@@ -10435,7 +10435,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M152" s="4" t="str">
-        <x:v>100x100</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N152" s="4" t="str">
         <x:v>svg</x:v>
@@ -10497,7 +10497,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M153" s="4" t="str">
-        <x:v>100x100</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N153" s="4" t="str">
         <x:v>svg</x:v>
@@ -10559,7 +10559,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M154" s="4" t="str">
-        <x:v>100x100</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N154" s="4" t="str">
         <x:v>svg</x:v>
@@ -10621,7 +10621,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M155" s="4" t="str">
-        <x:v>100x100</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N155" s="4" t="str">
         <x:v>svg</x:v>
@@ -10683,7 +10683,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M156" s="4" t="str">
-        <x:v>100x100</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N156" s="4" t="str">
         <x:v>svg</x:v>
@@ -10745,7 +10745,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M157" s="4" t="str">
-        <x:v>100x100</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N157" s="4" t="str">
         <x:v>svg</x:v>
@@ -13673,16 +13673,16 @@
         <x:v>Figure P04-1</x:v>
       </x:c>
       <x:c r="K204" s="4" t="str">
-        <x:v>docs/images/part14/p04_01_project_positioning.png</x:v>
+        <x:v>docs/images/part14/p04/p04_01_project_positioning.svg</x:v>
       </x:c>
       <x:c r="L204" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M204" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N204" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O204" s="4" t="str">
         <x:v>Synthetic Mathematics and Code Textbook Factory Project Positioning Diagram.</x:v>
@@ -13735,16 +13735,16 @@
         <x:v>Figure P04-2</x:v>
       </x:c>
       <x:c r="K205" s="4" t="str">
-        <x:v>docs/images/part14/p04_02_goals_and_scope.png</x:v>
+        <x:v>docs/images/part14/p04/p04_02_goals_and_scope.svg</x:v>
       </x:c>
       <x:c r="L205" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M205" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N205" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O205" s="4" t="str">
         <x:v>P04 Project Objectives and Scope Diagram.</x:v>
@@ -13797,16 +13797,16 @@
         <x:v>Figure P04-3</x:v>
       </x:c>
       <x:c r="K206" s="4" t="str">
-        <x:v>docs/images/part14/p04_03_pipeline_overview.png</x:v>
+        <x:v>docs/images/part14/p04/p04_03_pipeline_overview.svg</x:v>
       </x:c>
       <x:c r="L206" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M206" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N206" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O206" s="4" t="str">
         <x:v>P04 Overall Architecture Overview Diagram.</x:v>
@@ -13861,16 +13861,16 @@
         <x:v>Figure P04-4</x:v>
       </x:c>
       <x:c r="K207" s="4" t="str">
-        <x:v>docs/images/part14/p04_04_roles_and_responsibilities.png</x:v>
+        <x:v>docs/images/part14/p04/p04_04_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L207" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M207" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>900x491</x:v>
       </x:c>
       <x:c r="N207" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O207" s="4" t="str">
         <x:v>Textbook Factory Responsibility Collaboration Diagram.</x:v>
@@ -13923,7 +13923,7 @@
         <x:v>Figure P04-5</x:v>
       </x:c>
       <x:c r="K208" s="4" t="str">
-        <x:v>docs/images/part14/p04_05_seed_to_plan.png</x:v>
+        <x:v>docs/images/part14/p04/p04_05_seed_to_plan.svg</x:v>
       </x:c>
       <x:c r="L208" s="4" t="str">
         <x:v>yes</x:v>
@@ -13932,7 +13932,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N208" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O208" s="4" t="str">
         <x:v>Mapping from Seed Problems to Chapter Plans.</x:v>
@@ -13985,16 +13985,16 @@
         <x:v>Figure P04-6</x:v>
       </x:c>
       <x:c r="K209" s="4" t="str">
-        <x:v>docs/images/part14/p04_06_evol_path.png</x:v>
+        <x:v>docs/images/part14/p04/p04_06_evol_path.svg</x:v>
       </x:c>
       <x:c r="L209" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M209" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N209" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O209" s="4" t="str">
         <x:v>Evol-Instruct Evolution Path Diagram.</x:v>
@@ -14047,16 +14047,16 @@
         <x:v>Figure P04-7</x:v>
       </x:c>
       <x:c r="K210" s="4" t="str">
-        <x:v>docs/images/part14/p04_07_cot_vs_pot.png</x:v>
+        <x:v>docs/images/part14/p04/p04_07_cot_vs_pot.svg</x:v>
       </x:c>
       <x:c r="L210" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M210" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N210" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O210" s="4" t="str">
         <x:v>CoT vs. PoT Comparison Diagram.</x:v>
@@ -14111,16 +14111,16 @@
         <x:v>Figure P04-8</x:v>
       </x:c>
       <x:c r="K211" s="4" t="str">
-        <x:v>docs/images/part14/p04_08_generation_chain.png</x:v>
+        <x:v>docs/images/part14/p04/p04_08_generation_chain.svg</x:v>
       </x:c>
       <x:c r="L211" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M211" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1296x724</x:v>
       </x:c>
       <x:c r="N211" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O211" s="4" t="str">
         <x:v>Generation Pipeline Detail Diagram.</x:v>
@@ -14175,16 +14175,16 @@
         <x:v>Figure P04-9</x:v>
       </x:c>
       <x:c r="K212" s="4" t="str">
-        <x:v>docs/images/part14/p04_09_sandbox_validation.png</x:v>
+        <x:v>docs/images/part14/p04/p04_09_sandbox_validation.svg</x:v>
       </x:c>
       <x:c r="L212" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M212" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1296x707</x:v>
       </x:c>
       <x:c r="N212" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O212" s="4" t="str">
         <x:v>Sandbox Validation Execution Path Diagram.</x:v>
@@ -14237,16 +14237,16 @@
         <x:v>Figure P04-10</x:v>
       </x:c>
       <x:c r="K213" s="4" t="str">
-        <x:v>docs/images/part14/p04_10_packaging_outputs.png</x:v>
+        <x:v>docs/images/part14/p04/p04_10_packaging_outputs.svg</x:v>
       </x:c>
       <x:c r="L213" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M213" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>900x503</x:v>
       </x:c>
       <x:c r="N213" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O213" s="4" t="str">
         <x:v>Textbook Packaging Artifact Relationship Diagram.</x:v>
@@ -14299,7 +14299,7 @@
         <x:v>Figure P04-11</x:v>
       </x:c>
       <x:c r="K214" s="4" t="str">
-        <x:v>docs/images/part14/p04_11_training_interface.png</x:v>
+        <x:v>docs/images/part14/p04/p04_11_training_interface.svg</x:v>
       </x:c>
       <x:c r="L214" s="4" t="str">
         <x:v>yes</x:v>
@@ -14308,7 +14308,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N214" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O214" s="4" t="str">
         <x:v>Training Encapsulation Interface Diagram.</x:v>
@@ -14361,7 +14361,7 @@
         <x:v>Figure P05-1</x:v>
       </x:c>
       <x:c r="K215" s="4" t="str">
-        <x:v>docs/images/part14/p05_01_overall_architecture.png</x:v>
+        <x:v>docs/images/part14/p05/p05_01_overall_architecture.svg</x:v>
       </x:c>
       <x:c r="L215" s="4" t="str">
         <x:v>yes</x:v>
@@ -14370,7 +14370,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N215" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O215" s="4" t="str">
         <x:v>Overall architecture diagram of the multimodal RAG financial report assistant.</x:v>
@@ -14425,7 +14425,7 @@
         <x:v>Figure P05-2</x:v>
       </x:c>
       <x:c r="K216" s="4" t="str">
-        <x:v>docs/images/part14/p05_02_vision_vs_ocr.png</x:v>
+        <x:v>docs/images/part14/p05/p05_02_vision_vs_ocr.svg</x:v>
       </x:c>
       <x:c r="L216" s="4" t="str">
         <x:v>yes</x:v>
@@ -14434,7 +14434,7 @@
         <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N216" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O216" s="4" t="str">
         <x:v>Comparison of Vision-First and OCR-First approaches.</x:v>
@@ -14489,7 +14489,7 @@
         <x:v>Figure P05-3</x:v>
       </x:c>
       <x:c r="K217" s="4" t="str">
-        <x:v>docs/images/part14/p05_03_page_assets.png</x:v>
+        <x:v>docs/images/part14/p05/p05_03_page_assets.svg</x:v>
       </x:c>
       <x:c r="L217" s="4" t="str">
         <x:v>yes</x:v>
@@ -14498,7 +14498,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N217" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O217" s="4" t="str">
         <x:v>Page assets and page number mapping diagram.</x:v>
@@ -14551,7 +14551,7 @@
         <x:v>Figure P05-4</x:v>
       </x:c>
       <x:c r="K218" s="4" t="str">
-        <x:v>docs/images/part14/p05_04_indexing_pipeline.png</x:v>
+        <x:v>docs/images/part14/p05/p05_04_indexing_pipeline.svg</x:v>
       </x:c>
       <x:c r="L218" s="4" t="str">
         <x:v>yes</x:v>
@@ -14560,7 +14560,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N218" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O218" s="4" t="str">
         <x:v>PDF page rendering and visual index construction diagram.</x:v>
@@ -14613,7 +14613,7 @@
         <x:v>Figure P05-5</x:v>
       </x:c>
       <x:c r="K219" s="4" t="str">
-        <x:v>docs/images/part14/p05_05_topk_filtering.png</x:v>
+        <x:v>docs/images/part14/p05/p05_05_topk_filtering.svg</x:v>
       </x:c>
       <x:c r="L219" s="4" t="str">
         <x:v>yes</x:v>
@@ -14622,7 +14622,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N219" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O219" s="4" t="str">
         <x:v>Top-K multi-page recall and table-of-contents page filtering diagram.</x:v>
@@ -14675,7 +14675,7 @@
         <x:v>Figure P05-6</x:v>
       </x:c>
       <x:c r="K220" s="4" t="str">
-        <x:v>docs/images/part14/p05_06_multi_image_prompting.png</x:v>
+        <x:v>docs/images/part14/p05/p05_06_multi_image_prompting.svg</x:v>
       </x:c>
       <x:c r="L220" s="4" t="str">
         <x:v>yes</x:v>
@@ -14684,7 +14684,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N220" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O220" s="4" t="str">
         <x:v>Multi-image context injection and answer constraint diagram.</x:v>
@@ -14737,7 +14737,7 @@
         <x:v>Figure P05-7</x:v>
       </x:c>
       <x:c r="K221" s="4" t="str">
-        <x:v>docs/images/part14/p05_07_eval_framework.png</x:v>
+        <x:v>docs/images/part14/p05/p05_07_eval_framework.svg</x:v>
       </x:c>
       <x:c r="L221" s="4" t="str">
         <x:v>yes</x:v>
@@ -14746,7 +14746,7 @@
         <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N221" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O221" s="4" t="str">
         <x:v>Dual-layer evaluation framework for retrieval and answer quality.</x:v>
@@ -14799,7 +14799,7 @@
         <x:v>Figure P05-8</x:v>
       </x:c>
       <x:c r="K222" s="4" t="str">
-        <x:v>docs/images/part14/p05_08_optimization_roadmap.png</x:v>
+        <x:v>docs/images/part14/p05/p05_08_optimization_roadmap.svg</x:v>
       </x:c>
       <x:c r="L222" s="4" t="str">
         <x:v>yes</x:v>
@@ -14808,7 +14808,7 @@
         <x:v>1800x1005</x:v>
       </x:c>
       <x:c r="N222" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O222" s="4" t="str">
         <x:v>Multimodal RAG optimization roadmap.</x:v>
@@ -14861,7 +14861,7 @@
         <x:v>Figure P05-9</x:v>
       </x:c>
       <x:c r="K223" s="4" t="str">
-        <x:v>docs/images/part14/p05_09_hybrid_rag.png</x:v>
+        <x:v>docs/images/part14/p05/p05_09_hybrid_rag.svg</x:v>
       </x:c>
       <x:c r="L223" s="4" t="str">
         <x:v>yes</x:v>
@@ -14870,7 +14870,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N223" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O223" s="4" t="str">
         <x:v>Collaborative architecture of text RAG and multimodal RAG.</x:v>
@@ -14925,7 +14925,7 @@
         <x:v>Figure P06-1</x:v>
       </x:c>
       <x:c r="K224" s="4" t="str">
-        <x:v>docs/images/part14/p06_01_prm_factory_overview.png</x:v>
+        <x:v>docs/images/part14/p06/p06_01_prm_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L224" s="4" t="str">
         <x:v>yes</x:v>
@@ -14934,7 +14934,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N224" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O224" s="4" t="str">
         <x:v>CoT and PRM Data Factory Overview.</x:v>
@@ -14987,16 +14987,16 @@
         <x:v>Figure P06-2</x:v>
       </x:c>
       <x:c r="K225" s="4" t="str">
-        <x:v>docs/images/part14/p06_02_step_validation_loop.png</x:v>
+        <x:v>docs/images/part14/p06/p06_02_step_validation_loop.svg</x:v>
       </x:c>
       <x:c r="L225" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M225" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N225" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O225" s="4" t="str">
         <x:v>Step-Level Validation and Training Feedback Loop.</x:v>
@@ -15049,7 +15049,7 @@
         <x:v>Figure P06-3</x:v>
       </x:c>
       <x:c r="K226" s="4" t="str">
-        <x:v>docs/images/part14/p06_03_task_sampling.png</x:v>
+        <x:v>docs/images/part14/p06/p06_03_task_sampling.svg</x:v>
       </x:c>
       <x:c r="L226" s="4" t="str">
         <x:v>yes</x:v>
@@ -15058,7 +15058,7 @@
         <x:v>1800x982</x:v>
       </x:c>
       <x:c r="N226" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O226" s="4" t="str">
         <x:v>Task Sampling and Specification Generation Flowchart.</x:v>
@@ -15111,16 +15111,16 @@
         <x:v>Figure P06-4</x:v>
       </x:c>
       <x:c r="K227" s="4" t="str">
-        <x:v>docs/images/part14/p06_04_trace_types.png</x:v>
+        <x:v>docs/images/part14/p06/p06_04_trace_types.svg</x:v>
       </x:c>
       <x:c r="L227" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M227" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>2752x1536</x:v>
       </x:c>
       <x:c r="N227" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O227" s="4" t="str">
         <x:v>Schematic of the Three Trajectory Types.</x:v>
@@ -15175,16 +15175,16 @@
         <x:v>Figure P06-5</x:v>
       </x:c>
       <x:c r="K228" s="4" t="str">
-        <x:v>docs/images/part14/p06_05_step_schema.png</x:v>
+        <x:v>docs/images/part14/p06/p06_05_step_schema.svg</x:v>
       </x:c>
       <x:c r="L228" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M228" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1344x734</x:v>
       </x:c>
       <x:c r="N228" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O228" s="4" t="str">
         <x:v>PRM Step Schema Schematic.</x:v>
@@ -15239,7 +15239,7 @@
         <x:v>Figure P06-6</x:v>
       </x:c>
       <x:c r="K229" s="4" t="str">
-        <x:v>docs/images/part14/p06_06_validation_pipeline.png</x:v>
+        <x:v>docs/images/part14/p06/p06_06_validation_pipeline.svg</x:v>
       </x:c>
       <x:c r="L229" s="4" t="str">
         <x:v>yes</x:v>
@@ -15248,7 +15248,7 @@
         <x:v>1400x764</x:v>
       </x:c>
       <x:c r="N229" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O229" s="4" t="str">
         <x:v>Step Validation and Result Comparison Pipeline.</x:v>
@@ -15303,16 +15303,16 @@
         <x:v>Figure P06-7</x:v>
       </x:c>
       <x:c r="K230" s="4" t="str">
-        <x:v>docs/images/part14/p06_07_step_labels.png</x:v>
+        <x:v>docs/images/part14/p06/p06_07_step_labels.svg</x:v>
       </x:c>
       <x:c r="L230" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M230" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N230" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O230" s="4" t="str">
         <x:v>Step Labels and Process-Only Signal Schematic.</x:v>
@@ -15367,7 +15367,7 @@
         <x:v>Figure P06-8</x:v>
       </x:c>
       <x:c r="K231" s="4" t="str">
-        <x:v>docs/images/part14/p06_08_training_interface.png</x:v>
+        <x:v>docs/images/part14/p06/p06_08_training_interface.svg</x:v>
       </x:c>
       <x:c r="L231" s="4" t="str">
         <x:v>yes</x:v>
@@ -15376,7 +15376,7 @@
         <x:v>1400x781</x:v>
       </x:c>
       <x:c r="N231" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O231" s="4" t="str">
         <x:v>PRM Data Packaging and Training Interface.</x:v>
@@ -15429,16 +15429,16 @@
         <x:v>Figure P06-9</x:v>
       </x:c>
       <x:c r="K232" s="4" t="str">
-        <x:v>docs/images/part14/p06_09_validation_metrics.png</x:v>
+        <x:v>docs/images/part14/p06/p06_09_validation_metrics.svg</x:v>
       </x:c>
       <x:c r="L232" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M232" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1280x720</x:v>
       </x:c>
       <x:c r="N232" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O232" s="4" t="str">
         <x:v>Validation Pass Rate vs. Trajectory Type Comparison.</x:v>
@@ -15493,16 +15493,16 @@
         <x:v>Figure P06-10</x:v>
       </x:c>
       <x:c r="K233" s="4" t="str">
-        <x:v>docs/images/part14/p06_10_noise_sources.png</x:v>
+        <x:v>docs/images/part14/p06/p06_10_noise_sources.svg</x:v>
       </x:c>
       <x:c r="L233" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M233" s="4" t="str">
-        <x:v>1400x781</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N233" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O233" s="4" t="str">
         <x:v>Noise Sources in Negative and Repair Trajectories.</x:v>
@@ -15555,16 +15555,16 @@
         <x:v>Figure P07-1</x:v>
       </x:c>
       <x:c r="K234" s="4" t="str">
-        <x:v>docs/images/part14/p07_01_agent_tooluse_factory_overview.png</x:v>
+        <x:v>docs/images/part14/p07/p07_01_agent_tooluse_factory_overview.svg</x:v>
       </x:c>
       <x:c r="L234" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M234" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N234" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O234" s="4" t="str">
         <x:v>Agent Tool-Use Data Factory Overview.</x:v>
@@ -15617,16 +15617,16 @@
         <x:v>Figure P07-2</x:v>
       </x:c>
       <x:c r="K235" s="4" t="str">
-        <x:v>docs/images/part14/p07_02_three_layer_architecture.png</x:v>
+        <x:v>docs/images/part14/p07/p07_02_three_layer_architecture.svg</x:v>
       </x:c>
       <x:c r="L235" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M235" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1699x926</x:v>
       </x:c>
       <x:c r="N235" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O235" s="4" t="str">
         <x:v>Agent Tool-Use Three-Layer Architecture Diagram.</x:v>
@@ -15681,16 +15681,16 @@
         <x:v>Figure P07-3</x:v>
       </x:c>
       <x:c r="K236" s="4" t="str">
-        <x:v>docs/images/part14/p07_03_roles_and_responsibilities.png</x:v>
+        <x:v>docs/images/part14/p07/p07_03_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L236" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M236" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N236" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O236" s="4" t="str">
         <x:v>Key Engineering Facets of the Agent Data Factory.</x:v>
@@ -15743,16 +15743,16 @@
         <x:v>Figure P07-4</x:v>
       </x:c>
       <x:c r="K237" s="4" t="str">
-        <x:v>docs/images/part14/p07_04_tool_schema_structure.png</x:v>
+        <x:v>docs/images/part14/p07/p07_04_tool_schema_structure.svg</x:v>
       </x:c>
       <x:c r="L237" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M237" s="4" t="str">
-        <x:v>1400x781</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N237" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O237" s="4" t="str">
         <x:v>Tool Schema Structure Diagram.</x:v>
@@ -15807,16 +15807,16 @@
         <x:v>Figure P07-5</x:v>
       </x:c>
       <x:c r="K238" s="4" t="str">
-        <x:v>docs/images/part14/p07_05_task_specs_and_templates.png</x:v>
+        <x:v>docs/images/part14/p07/p07_05_task_specs_and_templates.svg</x:v>
       </x:c>
       <x:c r="L238" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M238" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1700x925</x:v>
       </x:c>
       <x:c r="N238" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O238" s="4" t="str">
         <x:v>Relationship Diagram of Task Specifications and Trajectory Templates.</x:v>
@@ -15869,16 +15869,16 @@
         <x:v>Figure P07-6</x:v>
       </x:c>
       <x:c r="K239" s="4" t="str">
-        <x:v>docs/images/part14/p07_06_trajectory_taxonomy.png</x:v>
+        <x:v>docs/images/part14/p07/p07_06_trajectory_taxonomy.svg</x:v>
       </x:c>
       <x:c r="L239" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M239" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1400x684</x:v>
       </x:c>
       <x:c r="N239" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O239" s="4" t="str">
         <x:v>success / recovery / block Trajectory Taxonomy Diagram.</x:v>
@@ -15931,16 +15931,16 @@
         <x:v>Figure P07-7</x:v>
       </x:c>
       <x:c r="K240" s="4" t="str">
-        <x:v>docs/images/part14/p07_07_simulated_env_loop.png</x:v>
+        <x:v>docs/images/part14/p07/p07_07_simulated_env_loop.svg</x:v>
       </x:c>
       <x:c r="L240" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M240" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N240" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O240" s="4" t="str">
         <x:v>Simulated Tool Environment Execution Closure Diagram.</x:v>
@@ -15993,7 +15993,7 @@
         <x:v>Figure P07-8</x:v>
       </x:c>
       <x:c r="K241" s="4" t="str">
-        <x:v>docs/images/part14/p07_08_pipeline_steps.png</x:v>
+        <x:v>docs/images/part14/p07/p07_08_pipeline_steps.svg</x:v>
       </x:c>
       <x:c r="L241" s="4" t="str">
         <x:v>yes</x:v>
@@ -16002,7 +16002,7 @@
         <x:v>1400x764</x:v>
       </x:c>
       <x:c r="N241" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O241" s="4" t="str">
         <x:v>P07 Six-Step Pipeline Diagram.</x:v>
@@ -16057,16 +16057,16 @@
         <x:v>Figure P07-9</x:v>
       </x:c>
       <x:c r="K242" s="4" t="str">
-        <x:v>docs/images/part14/p07_09_recovery_flow.png</x:v>
+        <x:v>docs/images/part14/p07/p07_09_recovery_flow.svg</x:v>
       </x:c>
       <x:c r="L242" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M242" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N242" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O242" s="4" t="str">
         <x:v>Parameter Correction and Retry Flow Diagram.</x:v>
@@ -16119,16 +16119,16 @@
         <x:v>Figure P07-10</x:v>
       </x:c>
       <x:c r="K243" s="4" t="str">
-        <x:v>docs/images/part14/p07_10_memory_trajectory.png</x:v>
+        <x:v>docs/images/part14/p07/p07_10_memory_trajectory.svg</x:v>
       </x:c>
       <x:c r="L243" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M243" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N243" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O243" s="4" t="str">
         <x:v>Memory Read/Write Trajectory Diagram.</x:v>
@@ -16181,16 +16181,16 @@
         <x:v>Figure P07-11</x:v>
       </x:c>
       <x:c r="K244" s="4" t="str">
-        <x:v>docs/images/part14/p07_11_unsafe_block.png</x:v>
+        <x:v>docs/images/part14/p07/p07_11_unsafe_block.svg</x:v>
       </x:c>
       <x:c r="L244" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M244" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1702x924</x:v>
       </x:c>
       <x:c r="N244" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O244" s="4" t="str">
         <x:v>Unsafe Block Decision Flow Diagram.</x:v>
@@ -16243,16 +16243,16 @@
         <x:v>Figure P07-12</x:v>
       </x:c>
       <x:c r="K245" s="4" t="str">
-        <x:v>docs/images/part14/p07_12_dataset_repacking.png</x:v>
+        <x:v>docs/images/part14/p07/p07_12_dataset_repacking.svg</x:v>
       </x:c>
       <x:c r="L245" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M245" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N245" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O245" s="4" t="str">
         <x:v>Event Log to Training Sample Reassembly Diagram.</x:v>
@@ -16305,16 +16305,16 @@
         <x:v>Figure P07-13</x:v>
       </x:c>
       <x:c r="K246" s="4" t="str">
-        <x:v>docs/images/part14/p07_13_eval_and_checks.png</x:v>
+        <x:v>docs/images/part14/p07/p07_13_eval_and_checks.svg</x:v>
       </x:c>
       <x:c r="L246" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M246" s="4" t="str">
-        <x:v>1400x781</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N246" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O246" s="4" t="str">
         <x:v>Evaluation and Inspection Dual-Closure Diagram.</x:v>
@@ -16367,16 +16367,16 @@
         <x:v>Figure P07-14</x:v>
       </x:c>
       <x:c r="K247" s="4" t="str">
-        <x:v>docs/images/part14/p07_14_roadmap.png</x:v>
+        <x:v>docs/images/part14/p07/p07_14_roadmap.svg</x:v>
       </x:c>
       <x:c r="L247" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M247" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N247" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O247" s="4" t="str">
         <x:v>P07 Future Evolution Roadmap.</x:v>
@@ -16429,16 +16429,16 @@
         <x:v>Figure 1: P08 DataOps platform overview</x:v>
       </x:c>
       <x:c r="K248" s="4" t="str">
-        <x:v>docs/images/part14/p08_01_dataops_platform_overview.png</x:v>
+        <x:v>docs/images/part14/p08/p08_01_dataops_platform_overview.svg</x:v>
       </x:c>
       <x:c r="L248" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M248" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N248" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O248" s="4" t="str">
         <x:v>Figure 1: P08 DataOps platform overview.</x:v>
@@ -16491,16 +16491,16 @@
         <x:v>Figure 2: Four-layer platform architecture</x:v>
       </x:c>
       <x:c r="K249" s="4" t="str">
-        <x:v>docs/images/part14/p08_02_four_layer_architecture.png</x:v>
+        <x:v>docs/images/part14/p08/p08_02_four_layer_architecture.svg</x:v>
       </x:c>
       <x:c r="L249" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M249" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N249" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O249" s="4" t="str">
         <x:v>Figure 2: Four-layer platform architecture.</x:v>
@@ -16555,16 +16555,16 @@
         <x:v>Figure 3: Spec generation, simulated run, evaluation, and check flow</x:v>
       </x:c>
       <x:c r="K250" s="4" t="str">
-        <x:v>docs/images/part14/p08_03_specs_to_ops_pipeline.png</x:v>
+        <x:v>docs/images/part14/p08/p08_03_specs_to_ops_pipeline.svg</x:v>
       </x:c>
       <x:c r="L250" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M250" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N250" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O250" s="4" t="str">
         <x:v>Figure 3: Specification generation, simulated operation, evaluation, and check flow.</x:v>
@@ -16617,16 +16617,16 @@
         <x:v>Figure 4: Tenant, project, role, and API relationship</x:v>
       </x:c>
       <x:c r="K251" s="4" t="str">
-        <x:v>docs/images/part14/p08_04_object_model.png</x:v>
+        <x:v>docs/images/part14/p08/p08_04_object_model.svg</x:v>
       </x:c>
       <x:c r="L251" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M251" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N251" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O251" s="4" t="str">
         <x:v>Figure 4: Tenant, project, role, and API relationship.</x:v>
@@ -16679,16 +16679,16 @@
         <x:v>Figure 5: Version lifecycle with release and rollback points</x:v>
       </x:c>
       <x:c r="K252" s="4" t="str">
-        <x:v>docs/images/part14/p08_05_version_lifecycle.png</x:v>
+        <x:v>docs/images/part14/p08/p08_05_version_lifecycle.svg</x:v>
       </x:c>
       <x:c r="L252" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M252" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N252" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O252" s="4" t="str">
         <x:v>Figure 5: Version lifecycle with release and rollback points.</x:v>
@@ -16741,16 +16741,16 @@
         <x:v>Figure 6: Experiment status distribution and governance actions</x:v>
       </x:c>
       <x:c r="K253" s="4" t="str">
-        <x:v>docs/images/part14/p08_06_experiment_tracking.png</x:v>
+        <x:v>docs/images/part14/p08/p08_06_experiment_tracking.svg</x:v>
       </x:c>
       <x:c r="L253" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M253" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x833</x:v>
       </x:c>
       <x:c r="N253" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O253" s="4" t="str">
         <x:v>Figure 6: Experiment status distribution and governance actions.</x:v>
@@ -16805,16 +16805,16 @@
         <x:v>Figure 7: Version, experiment, result, and rollback lineage</x:v>
       </x:c>
       <x:c r="K254" s="4" t="str">
-        <x:v>docs/images/part14/p08_07_lineage_graph.png</x:v>
+        <x:v>docs/images/part14/p08/p08_07_lineage_graph.svg</x:v>
       </x:c>
       <x:c r="L254" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M254" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N254" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O254" s="4" t="str">
         <x:v>Figure 7: Version, experiment, result, and rollback lineage.</x:v>
@@ -16867,16 +16867,16 @@
         <x:v>Figure 8: Rollback trigger and recovery flow</x:v>
       </x:c>
       <x:c r="K255" s="4" t="str">
-        <x:v>docs/images/part14/p08_08_rollback_flow.png</x:v>
+        <x:v>docs/images/part14/p08/p08_08_rollback_flow.svg</x:v>
       </x:c>
       <x:c r="L255" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M255" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N255" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O255" s="4" t="str">
         <x:v>Figure 8: Rollback trigger and recovery flow.</x:v>
@@ -16929,16 +16929,16 @@
         <x:v>Figure 9: Metrics, logs, alerts, and audit loop</x:v>
       </x:c>
       <x:c r="K256" s="4" t="str">
-        <x:v>docs/images/part14/p08_09_observability_loop.png</x:v>
+        <x:v>docs/images/part14/p08/p08_09_observability_loop.svg</x:v>
       </x:c>
       <x:c r="L256" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M256" s="4" t="str">
-        <x:v>1400x1400</x:v>
+        <x:v>1254x1254</x:v>
       </x:c>
       <x:c r="N256" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O256" s="4" t="str">
         <x:v>Figure 9: Metrics, logs, alerts, and audit loop.</x:v>
@@ -16991,16 +16991,16 @@
         <x:v>Figure 10: Audit logs and incident review</x:v>
       </x:c>
       <x:c r="K257" s="4" t="str">
-        <x:v>docs/images/part14/p08_10_audit_and_incident_review.png</x:v>
+        <x:v>docs/images/part14/p08/p08_10_audit_and_incident_review.svg</x:v>
       </x:c>
       <x:c r="L257" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M257" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N257" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O257" s="4" t="str">
         <x:v>Figure 10: Audit logs and incident review.</x:v>
@@ -17053,16 +17053,16 @@
         <x:v>Figure 11: Check pipeline and consistency validation</x:v>
       </x:c>
       <x:c r="K258" s="4" t="str">
-        <x:v>docs/images/part14/p08_11_validation_pipeline.png</x:v>
+        <x:v>docs/images/part14/p08/p08_11_validation_pipeline.svg</x:v>
       </x:c>
       <x:c r="L258" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M258" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N258" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O258" s="4" t="str">
         <x:v>Figure 11: Check pipeline and consistency validation.</x:v>
@@ -17117,16 +17117,16 @@
         <x:v>Figure P09-1</x:v>
       </x:c>
       <x:c r="K259" s="4" t="str">
-        <x:v>docs/images/part14/p09_01_privacy_pipeline_overview.png</x:v>
+        <x:v>docs/images/part14/p09/p09_01_privacy_pipeline_overview.svg</x:v>
       </x:c>
       <x:c r="L259" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M259" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N259" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O259" s="4" t="str">
         <x:v>P09 Privacy-Preserving Data Pipeline Overall Architecture.</x:v>
@@ -17181,16 +17181,16 @@
         <x:v>Figure P09-2</x:v>
       </x:c>
       <x:c r="K260" s="4" t="str">
-        <x:v>docs/images/part14/p09_02_roles_and_responsibilities.png</x:v>
+        <x:v>docs/images/part14/p09/p09_02_roles_and_responsibilities.svg</x:v>
       </x:c>
       <x:c r="L260" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M260" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N260" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O260" s="4" t="str">
         <x:v>Key Engineering Dimensions of the P09 Privacy Pipeline.</x:v>
@@ -17245,16 +17245,16 @@
         <x:v>Figure P09-3</x:v>
       </x:c>
       <x:c r="K261" s="4" t="str">
-        <x:v>docs/images/part14/p09_03_specs_layer.png</x:v>
+        <x:v>docs/images/part14/p09/p09_03_specs_layer.svg</x:v>
       </x:c>
       <x:c r="L261" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M261" s="4" t="str">
-        <x:v>1400x781</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N261" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O261" s="4" t="str">
         <x:v>Relationships Among the Four Artifact Types in the Privacy Specification Layer.</x:v>
@@ -17307,16 +17307,16 @@
         <x:v>Figure P09-4</x:v>
       </x:c>
       <x:c r="K262" s="4" t="str">
-        <x:v>docs/images/part14/p09_04_raw_records_coverage.png</x:v>
+        <x:v>docs/images/part14/p09/p09_04_raw_records_coverage.svg</x:v>
       </x:c>
       <x:c r="L262" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M262" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N262" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O262" s="4" t="str">
         <x:v>Scenario Coverage of Raw Sensitive Records.</x:v>
@@ -17369,16 +17369,16 @@
         <x:v>Figure P09-5</x:v>
       </x:c>
       <x:c r="K263" s="4" t="str">
-        <x:v>docs/images/part14/p09_05_pii_detection_distribution.png</x:v>
+        <x:v>docs/images/part14/p09/p09_05_pii_detection_distribution.svg</x:v>
       </x:c>
       <x:c r="L263" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M263" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N263" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O263" s="4" t="str">
         <x:v>PII Detection Rules and Hit Distribution.</x:v>
@@ -17433,16 +17433,16 @@
         <x:v>Figure P09-6</x:v>
       </x:c>
       <x:c r="K264" s="4" t="str">
-        <x:v>docs/images/part14/p09_06_classification_and_quarantine.png</x:v>
+        <x:v>docs/images/part14/p09/p09_06_classification_and_quarantine.svg</x:v>
       </x:c>
       <x:c r="L264" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M264" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N264" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O264" s="4" t="str">
         <x:v>Classification Determination and Quarantine Trigger Relationship.</x:v>
@@ -17495,16 +17495,16 @@
         <x:v>Figure P09-7</x:v>
       </x:c>
       <x:c r="K265" s="4" t="str">
-        <x:v>docs/images/part14/p09_07_redaction_strategies.png</x:v>
+        <x:v>docs/images/part14/p09/p09_07_redaction_strategies.svg</x:v>
       </x:c>
       <x:c r="L265" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M265" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N265" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O265" s="4" t="str">
         <x:v>De-identification Strategies for Different PII Types.</x:v>
@@ -17557,16 +17557,16 @@
         <x:v>Figure P09-8</x:v>
       </x:c>
       <x:c r="K266" s="4" t="str">
-        <x:v>docs/images/part14/p09_08_storage_zones.png</x:v>
+        <x:v>docs/images/part14/p09/p09_08_storage_zones.svg</x:v>
       </x:c>
       <x:c r="L266" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M266" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N266" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O266" s="4" t="str">
         <x:v>Storage Zones and Role Access Boundaries.</x:v>
@@ -17619,16 +17619,16 @@
         <x:v>Figure P09-9</x:v>
       </x:c>
       <x:c r="K267" s="4" t="str">
-        <x:v>docs/images/part14/p09_09_alerts_and_audit.png</x:v>
+        <x:v>docs/images/part14/p09/p09_09_alerts_and_audit.svg</x:v>
       </x:c>
       <x:c r="L267" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M267" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N267" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O267" s="4" t="str">
         <x:v>Relationships Among Alerts, Audit, and Incident Response.</x:v>
@@ -17681,16 +17681,16 @@
         <x:v>Figure P09-10</x:v>
       </x:c>
       <x:c r="K268" s="4" t="str">
-        <x:v>docs/images/part14/p09_10_preflight_checks.png</x:v>
+        <x:v>docs/images/part14/p09/p09_10_preflight_checks.svg</x:v>
       </x:c>
       <x:c r="L268" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M268" s="4" t="str">
-        <x:v>1400x781</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N268" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O268" s="4" t="str">
         <x:v>Preflight Check Process. Because it reflects a mature engineering practice: Not "run first, then observe," but "confirm that minimum conditions are met first, then proceed to higher-risk processing and exercise stages." Figure P09-10: Preflight Check Process --- Many case studies describe only the success path, not the failure path.</x:v>
@@ -17743,16 +17743,16 @@
         <x:v>Figure P09-11</x:v>
       </x:c>
       <x:c r="K269" s="4" t="str">
-        <x:v>docs/images/part14/p09_11_incident_postmortem.png</x:v>
+        <x:v>docs/images/part14/p09/p09_11_incident_postmortem.svg</x:v>
       </x:c>
       <x:c r="L269" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M269" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N269" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O269" s="4" t="str">
         <x:v>Incident Response and Postmortem Feedback Loop.</x:v>
@@ -17805,16 +17805,16 @@
         <x:v>Figure P09-12</x:v>
       </x:c>
       <x:c r="K270" s="4" t="str">
-        <x:v>docs/images/part14/p09_12_execution_sequence.png</x:v>
+        <x:v>docs/images/part14/p09/p09_12_execution_sequence.svg</x:v>
       </x:c>
       <x:c r="L270" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M270" s="4" t="str">
-        <x:v>1400x764</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N270" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O270" s="4" t="str">
         <x:v>P09 Minimal Reproducible Execution Chain.</x:v>
@@ -17867,16 +17867,16 @@
         <x:v>Figure 1: End-to-end LLM data flywheel overview</x:v>
       </x:c>
       <x:c r="K271" s="4" t="str">
-        <x:v>docs/images/part14/p10_01_flywheel_overview.png</x:v>
+        <x:v>docs/images/part14/p10/p10_01_flywheel_overview.svg</x:v>
       </x:c>
       <x:c r="L271" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M271" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N271" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O271" s="4" t="str">
         <x:v>From an engineering perspective, this project should be viewed as five layers instead of a linear data-input to model-output chain.</x:v>
@@ -17927,16 +17927,16 @@
         <x:v>Figure 2: Upstream project registry and interface mapping</x:v>
       </x:c>
       <x:c r="K272" s="4" t="str">
-        <x:v>docs/images/part14/p10_02_registry_and_interfaces.png</x:v>
+        <x:v>docs/images/part14/p10/p10_02_registry_and_interfaces.svg</x:v>
       </x:c>
       <x:c r="L272" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M272" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N272" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O272" s="4" t="str">
         <x:v>Figure 2: Upstream project registry and interface mapping.</x:v>
@@ -17987,16 +17987,16 @@
         <x:v>Figure 3: Structured upstream project specs</x:v>
       </x:c>
       <x:c r="K273" s="4" t="str">
-        <x:v>docs/images/part14/p10_03_project_specs.png</x:v>
+        <x:v>docs/images/part14/p10/p10_03_project_specs.svg</x:v>
       </x:c>
       <x:c r="L273" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M273" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N273" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O273" s="4" t="str">
         <x:v>Figure 3: Structured upstream project specs.</x:v>
@@ -18047,16 +18047,16 @@
         <x:v>Figure 4: Five-stage plan and milestone relationships</x:v>
       </x:c>
       <x:c r="K274" s="4" t="str">
-        <x:v>docs/images/part14/p10_04_stage_plan.png</x:v>
+        <x:v>docs/images/part14/p10/p10_04_stage_plan.svg</x:v>
       </x:c>
       <x:c r="L274" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M274" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1672x642</x:v>
       </x:c>
       <x:c r="N274" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O274" s="4" t="str">
         <x:v>Figure 4: Five-stage plan and milestone relationships.</x:v>
@@ -18107,16 +18107,16 @@
         <x:v>Figure 5: Five-layer flywheel code mapping</x:v>
       </x:c>
       <x:c r="K275" s="4" t="str">
-        <x:v>docs/images/part14/p10_05_architecture_code_mapping.png</x:v>
+        <x:v>docs/images/part14/p10/p10_05_architecture_code_mapping.svg</x:v>
       </x:c>
       <x:c r="L275" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M275" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N275" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O275" s="4" t="str">
         <x:v>Figure 5: Five-layer flywheel code mapping.</x:v>
@@ -18167,16 +18167,16 @@
         <x:v>Figure 6: System boundaries and control points</x:v>
       </x:c>
       <x:c r="K276" s="4" t="str">
-        <x:v>docs/images/part14/p10_06_boundaries_and_control_points.png</x:v>
+        <x:v>docs/images/part14/p10/p10_06_boundaries_and_control_points.svg</x:v>
       </x:c>
       <x:c r="L276" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M276" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1586x992</x:v>
       </x:c>
       <x:c r="N276" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O276" s="4" t="str">
         <x:v>Figure 6: System boundaries and control points.</x:v>
@@ -18227,16 +18227,16 @@
         <x:v>Figure 7: Run records and milestone board</x:v>
       </x:c>
       <x:c r="K277" s="4" t="str">
-        <x:v>docs/images/part14/p10_07_runs_and_milestones.png</x:v>
+        <x:v>docs/images/part14/p10/p10_07_runs_and_milestones.svg</x:v>
       </x:c>
       <x:c r="L277" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M277" s="4" t="str">
-        <x:v>1800x1005</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N277" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O277" s="4" t="str">
         <x:v>Figure 7: Run records and milestone board.</x:v>
@@ -18287,16 +18287,16 @@
         <x:v>Figure 8: Flywheel bottleneck map</x:v>
       </x:c>
       <x:c r="K278" s="4" t="str">
-        <x:v>docs/images/part14/p10_08_bottleneck_map.png</x:v>
+        <x:v>docs/images/part14/p10/p10_08_bottleneck_map.svg</x:v>
       </x:c>
       <x:c r="L278" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M278" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1536x1024</x:v>
       </x:c>
       <x:c r="N278" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O278" s="4" t="str">
         <x:v>Figure 8: Flywheel bottleneck map.</x:v>
@@ -18347,16 +18347,16 @@
         <x:v>Figure 9: System-level metric generation logic</x:v>
       </x:c>
       <x:c r="K279" s="4" t="str">
-        <x:v>docs/images/part14/p10_09_metrics_codegen.png</x:v>
+        <x:v>docs/images/part14/p10/p10_09_metrics_codegen.svg</x:v>
       </x:c>
       <x:c r="L279" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M279" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N279" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O279" s="4" t="str">
         <x:v>Figure 9: System-level metric generation logic.</x:v>
@@ -18407,16 +18407,16 @@
         <x:v>Figure 10: Check scripts and system contracts</x:v>
       </x:c>
       <x:c r="K280" s="4" t="str">
-        <x:v>docs/images/part14/p10_10_check_contracts.png</x:v>
+        <x:v>docs/images/part14/p10/p10_10_check_contracts.svg</x:v>
       </x:c>
       <x:c r="L280" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M280" s="4" t="str">
-        <x:v>1800x982</x:v>
+        <x:v>1672x941</x:v>
       </x:c>
       <x:c r="N280" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O280" s="4" t="str">
         <x:v>Figure 10: Check scripts and system contracts.</x:v>
@@ -18533,16 +18533,16 @@
         <x:v>Figure P12-1</x:v>
       </x:c>
       <x:c r="K282" s="4" t="str">
-        <x:v>docs/images/part14/p12_r1_reasoning_flywheel_architecture.png</x:v>
+        <x:v>docs/images/part14/p12/p12_r1_reasoning_flywheel_architecture.svg</x:v>
       </x:c>
       <x:c r="L282" s="4" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="M282" s="4" t="str">
-        <x:v>2816x1362</x:v>
+        <x:v>1774x887</x:v>
       </x:c>
       <x:c r="N282" s="4" t="str">
-        <x:v>png</x:v>
+        <x:v>svg</x:v>
       </x:c>
       <x:c r="O282" s="4" t="str">
         <x:v>The closed-loop structure from cold-start data extraction, multi-path reasoning sampling, verifier pool, and rejection sampling to second-round SFT merging and training evaluation.</x:v>
